--- a/第8回_Loss_Learning/excel_loss_learning_demo.xlsx
+++ b/第8回_Loss_Learning/excel_loss_learning_demo.xlsx
@@ -99,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -121,11 +121,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00D8DEE9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -157,6 +163,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +544,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Excelで体験する言語モデルのしくみ 第8回 Lossと学習</t>
         </is>
@@ -660,7 +669,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>12_TROUBLE: よくある確認点</t>
         </is>
@@ -685,7 +694,7 @@
           <t>よくある確認点</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -774,7 +783,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>13_SERIES_ROADMAP</t>
         </is>
@@ -801,8 +810,8 @@
           <t>全10回ロードマップ</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1022,7 +1031,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>01_INPUT: Loss計算に使う正解tokenと学習設定</t>
         </is>
@@ -1055,15 +1064,15 @@
           <t>第7回のSoftmax結果に正解tokenを重ね、予測のズレをLossとして数値化します。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1083,7 +1092,7 @@
           <t>文脈token</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="4" t="inlineStr">
@@ -1091,8 +1100,8 @@
           <t>候補tokenと初期logit</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
@@ -1283,8 +1292,8 @@
           <t>学習設定</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
@@ -1418,7 +1427,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>02_PROB_LOSS: 正解tokenの確率からLossを計算する</t>
         </is>
@@ -1449,14 +1458,14 @@
           <t>Cross Entropy Lossは、正解tokenに割り当てた確率が低いほど大きくなります。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1475,10 +1484,10 @@
           <t>予測確率とLoss</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
@@ -1674,7 +1683,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>03_TARGET_GRADIENT: targetとの差が更新方向になる</t>
         </is>
@@ -1705,14 +1714,14 @@
           <t>SoftmaxとCross Entropyを組み合わせると、logitへの勾配は probability - target と読めます。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1731,11 +1740,11 @@
           <t>gradient = probability - target</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -1956,7 +1965,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>04_LEARNING_STEP: 1ステップ更新で正解確率が上がる</t>
         </is>
@@ -1987,14 +1996,14 @@
           <t>target_tokenのlogitを上げ、他候補を少し下げると、正解確率が上がりLossが下がります。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -2013,11 +2022,11 @@
           <t>更新前後の比較</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -2224,9 +2233,9 @@
           <t>Loss summary</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
@@ -2338,7 +2347,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>05_TRAINING_TRACE: 更新を繰り返すとLossが下がる</t>
         </is>
@@ -2369,14 +2378,14 @@
           <t>同じ簡略更新を数回繰り返し、target_probabilityとlossの変化を見ます。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -2395,9 +2404,9 @@
           <t>学習trace</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
@@ -2554,7 +2563,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>06_LEARNING_FLOW: Lossから学習へつながる流れ</t>
         </is>
@@ -2581,8 +2590,8 @@
           <t>学習フロー</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2713,7 +2722,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>10_RUN_PYTHON: Python in Excel 実行手順</t>
         </is>
@@ -2738,7 +2747,7 @@
           <t>実行手順</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2827,7 +2836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:A92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="142" customWidth="1" min="1" max="1"/>
@@ -2839,559 +2848,590 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>11_PYTHON_CODE: Python in Excelへ貼り付けるコード</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>外部 .py ファイルと同じ内容です。Excelの入力表を xl(...) で参照します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>import pandas as pd</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>import numpy as np</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-    </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>context_tokens = ["今日", "猫", "ごはん", "食べる"]</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>vocab = ["です", "ました", "ね", "よ", "犬", "走る"]</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>context_source_df = xl("'01_INPUT'!A6:B12", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>initial_logits = np.array([2.2, 1.5, 0.9, 0.4, -0.2, -0.8], dtype=float)</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>candidate_source_df = xl("'01_INPUT'!E6:G12", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>target_token = "ました"</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>settings_source_df = xl("'01_INPUT'!A15:C18", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>learning_rate = 0.8</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>training_steps = 4</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>context_tokens = context_source_df["token"].dropna().astype(str).tolist()</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vocab = candidate_source_df["candidate_token"].astype(str).tolist()</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>initial_logits = candidate_source_df["initial_logit"].astype(float).to_numpy()</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>settings = dict(zip(settings_source_df["parameter"].astype(str), settings_source_df["value"]))</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>target_token = str(settings.get("target_token", candidate_source_df.loc[candidate_source_df["target"].notna(), "candidate_token"].iloc[0]))</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>learning_rate = float(settings.get("learning_rate", 0.8))</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>training_steps = int(float(settings.get("training_steps", 4)))</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>def softmax(values):</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve">    shifted = values - values.max()</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">    exps = np.exp(shifted)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">    return exps / exps.sum()</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>def cross_entropy(probability):</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t xml:space="preserve">    return -np.log(probability)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>target_index = vocab.index(target_token)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>probabilities = softmax(initial_logits)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>loss = cross_entropy(probabilities[target_index])</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>one_hot = np.zeros(len(vocab))</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>one_hot[target_index] = 1.0</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>gradients = probabilities - one_hot</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>updated_logits = initial_logits - learning_rate * gradients</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>updated_probabilities = softmax(updated_logits)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>updated_loss = cross_entropy(updated_probabilities[target_index])</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>prediction_df = pd.DataFrame({</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t xml:space="preserve">    "candidate_token": vocab,</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t xml:space="preserve">    "logit_before": np.round(initial_logits, 4),</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_before": np.round(probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t xml:space="preserve">    "is_target": one_hot.astype(int),</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t xml:space="preserve">    "target_loss": [round(float(loss), 4) if i == target_index else "" for i in range(len(vocab))],</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>})</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" t="inlineStr"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>gradient_df = pd.DataFrame({</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t xml:space="preserve">    "candidate_token": vocab,</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_before": np.round(probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t xml:space="preserve">    "is_target": one_hot.astype(int),</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t xml:space="preserve">    "gradient_prob_minus_target": np.round(gradients, 4),</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">    "logit_delta": np.round(-learning_rate * gradients, 4),</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t xml:space="preserve">    "logit_after": np.round(updated_logits, 4),</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>})</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" t="inlineStr"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>learning_step_df = pd.DataFrame({</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t xml:space="preserve">    "candidate_token": vocab,</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t xml:space="preserve">    "logit_before": np.round(initial_logits, 4),</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_before": np.round(probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t xml:space="preserve">    "logit_after": np.round(updated_logits, 4),</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_after": np.round(updated_probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_change": np.round(updated_probabilities - probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>})</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" t="inlineStr"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>trace_rows = []</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>current_logits = initial_logits.copy()</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>for step in range(training_steps + 1):</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t xml:space="preserve">    current_probs = softmax(current_logits)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t xml:space="preserve">    current_loss = cross_entropy(current_probs[target_index])</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t xml:space="preserve">    trace_rows.append({</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t xml:space="preserve">        "step": step,</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t xml:space="preserve">        "target_logit": round(float(current_logits[target_index]), 4),</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t xml:space="preserve">        "target_probability": round(float(current_probs[target_index]), 4),</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t xml:space="preserve">        "loss": round(float(current_loss), 4),</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t xml:space="preserve">    })</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t xml:space="preserve">    if step &lt; training_steps:</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t xml:space="preserve">        current_one_hot = np.zeros(len(vocab))</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t xml:space="preserve">        current_one_hot[target_index] = 1.0</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t xml:space="preserve">        current_logits = current_logits - learning_rate * (current_probs - current_one_hot)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" t="inlineStr"/>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>loss_trace_df = pd.DataFrame(trace_rows)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>summary_df = pd.DataFrame([</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"state": "before", "target_token": target_token, "target_probability": round(float(probabilities[target_index]), 4), "loss": round(float(loss), 4)},</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"state": "after one step", "target_token": target_token, "target_probability": round(float(updated_probabilities[target_index]), 4), "loss": round(float(updated_loss), 4)},</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>])</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" t="inlineStr"/>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t># Python in Excelで最後に表示したい表を選びます。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>result_df = prediction_df</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t># result_df = gradient_df</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t># result_df = learning_step_df</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t># result_df = loss_trace_df</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t># result_df = summary_df</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="3" t="inlineStr"/>
-    </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>result_df</t>
         </is>

--- a/第8回_Loss_Learning/excel_loss_learning_demo.xlsx
+++ b/第8回_Loss_Learning/excel_loss_learning_demo.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -166,6 +166,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,7 +695,7 @@
       <c r="B3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>よくある確認点</t>
         </is>
@@ -805,7 +811,7 @@
       <c r="C3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>全10回ロードマップ</t>
         </is>
@@ -1059,7 +1065,7 @@
       <c r="J2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>第7回のSoftmax結果に正解tokenを重ね、予測のズレをLossとして数値化します。</t>
         </is>
@@ -1087,7 +1093,7 @@
       <c r="J4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>文脈token</t>
         </is>
@@ -1095,7 +1101,7 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>候補tokenと初期logit</t>
         </is>
@@ -1287,7 +1293,7 @@
       <c r="J13" s="3" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>学習設定</t>
         </is>
@@ -1453,7 +1459,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Cross Entropy Lossは、正解tokenに割り当てた確率が低いほど大きくなります。</t>
         </is>
@@ -1479,7 +1485,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>予測確率とLoss</t>
         </is>
@@ -1709,7 +1715,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>SoftmaxとCross Entropyを組み合わせると、logitへの勾配は probability - target と読めます。</t>
         </is>
@@ -1735,7 +1741,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>gradient = probability - target</t>
         </is>
@@ -1991,7 +1997,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>target_tokenのlogitを上げ、他候補を少し下げると、正解確率が上がりLossが下がります。</t>
         </is>
@@ -2017,7 +2023,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>更新前後の比較</t>
         </is>
@@ -2228,7 +2234,7 @@
       <c r="I13" s="3" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Loss summary</t>
         </is>
@@ -2373,7 +2379,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>同じ簡略更新を数回繰り返し、target_probabilityとlossの変化を見ます。</t>
         </is>
@@ -2399,7 +2405,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>学習trace</t>
         </is>
@@ -2585,7 +2591,7 @@
       <c r="C3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>学習フロー</t>
         </is>
@@ -2742,7 +2748,7 @@
       <c r="B3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>実行手順</t>
         </is>
@@ -2836,7 +2842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A92"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="142" customWidth="1" min="1" max="1"/>
@@ -2876,9 +2882,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6" ht="24" customHeight="1"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -2900,9 +2904,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" t="inlineStr"/>
-    </row>
+    <row r="10" ht="24" customHeight="1"/>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -2952,9 +2954,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" t="inlineStr"/>
-    </row>
+    <row r="18" ht="24" customHeight="1"/>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
@@ -2983,9 +2983,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" t="inlineStr"/>
-    </row>
+    <row r="23" ht="24" customHeight="1"/>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
@@ -3000,9 +2998,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" t="inlineStr"/>
-    </row>
+    <row r="26" ht="24" customHeight="1"/>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
@@ -3066,9 +3062,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" t="inlineStr"/>
-    </row>
+    <row r="36" ht="24" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
@@ -3118,9 +3112,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" t="inlineStr"/>
-    </row>
+    <row r="44" ht="24" customHeight="1"/>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
@@ -3177,9 +3169,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" t="inlineStr"/>
-    </row>
+    <row r="53" ht="24" customHeight="1"/>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
@@ -3236,9 +3226,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" t="inlineStr"/>
-    </row>
+    <row r="62" ht="24" customHeight="1"/>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
@@ -3344,9 +3332,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" t="inlineStr"/>
-    </row>
+    <row r="78" ht="24" customHeight="1"/>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
@@ -3382,9 +3368,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" t="inlineStr"/>
-    </row>
+    <row r="84" ht="24" customHeight="1"/>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
@@ -3427,9 +3411,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-    </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
